--- a/fixtures/idea_exports/Seldom Account Entries.xlsx
+++ b/fixtures/idea_exports/Seldom Account Entries.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,24 +476,24 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63</v>
+        <v>203</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45658</v>
+        <v>45660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Suspense Account 6</t>
+          <t>Suspense Account 22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sales invoice</t>
+          <t>Utility bill</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -505,29 +505,29 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>25284.89</v>
+        <v>76684.47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>143</v>
+        <v>1028</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45659</v>
+        <v>45677</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Suspense Account 41</t>
+          <t>Suspense Account 20</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Write off - settlement</t>
+          <t>Accrual</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -536,32 +536,32 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>28456.75</v>
       </c>
       <c r="H3" t="n">
-        <v>48999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1374</v>
+        <v>2206</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45682</v>
+        <v>45698</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Suspense Account 40</t>
+          <t>Suspense Account 26</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Supplier payment</t>
+          <t>Prepayment release</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -573,38 +573,38 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>50000</v>
+        <v>59415.07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1378</v>
+        <v>2488</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45683</v>
+        <v>45702</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Suspense Account 8</t>
+          <t>Suspense Account 49</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Monthly payroll</t>
+          <t>Cash advance, no invoice</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>30000</v>
+        <v>102999</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -612,53 +612,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1804</v>
+        <v>3348</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45689</v>
+        <v>45720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Suspense Account 33</t>
+          <t>Suspense Account 9</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Supplier payment</t>
+          <t>Write off - settlement</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>54999</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>87999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1925</v>
+        <v>4507</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45692</v>
+        <v>45741</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Suspense Account 14</t>
+          <t>Suspense Account 47</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Consultancy fee (related party)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -668,31 +668,31 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>10000</v>
+        <v>29565.46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2212</v>
+        <v>5465</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45698</v>
+        <v>45759</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Suspense Account 26</t>
+          <t>Suspense Account 45</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Prepayment release</t>
+          <t>Correction entry - reversal</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -702,26 +702,26 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>75370.53</v>
       </c>
       <c r="H8" t="n">
-        <v>35565.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2319</v>
+        <v>5807</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45700</v>
+        <v>45765</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Suspense Account 30</t>
+          <t>Suspense Account 46</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -731,16 +731,16 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>30000</v>
+        <v>14999</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -748,14 +748,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3648</v>
+        <v>6201</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45724</v>
+        <v>45774</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Suspense Account 37</t>
+          <t>Suspense Account 17</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -774,41 +774,41 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>31999</v>
       </c>
       <c r="H10" t="n">
-        <v>54999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4026</v>
+        <v>6977</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45731</v>
+        <v>45788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Suspense Account 21</t>
+          <t>Suspense Account 38</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Utility bill</t>
+          <t>Adjustment per director</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>150000</v>
+        <v>27999</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -816,33 +816,33 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4720</v>
+        <v>7390</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45744</v>
+        <v>45796</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Suspense Account 43</t>
+          <t>Suspense Account 13</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cash advance, no invoice</t>
+          <t>Write off - settlement</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>60000</v>
+        <v>133999</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -850,33 +850,33 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5474</v>
+        <v>7824</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45759</v>
+        <v>45803</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Suspense Account 18</t>
+          <t>Suspense Account 44</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Write off - settlement</t>
+          <t>Sales invoice</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>14401.63</v>
+        <v>62999</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -884,58 +884,58 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6019</v>
+        <v>7965</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45770</v>
+        <v>45805</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Suspense Account 36</t>
+          <t>Suspense Account 44</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Purchase invoice</t>
+          <t>Write off - settlement</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_b</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>170000</v>
+        <v>31224.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6863</v>
+        <v>8136</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45785</v>
+        <v>45809</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Suspense Account 17</t>
+          <t>Suspense Account 41</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Accrual</t>
+          <t>Prepayment release</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -947,19 +947,19 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>48764.52</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>7950</v>
+        <v>8627</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45805</v>
+        <v>45818</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Suspense Account 1</t>
+          <t>Suspense Account 37</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -969,31 +969,31 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>58265.84</v>
+        <v>170000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>7978</v>
+        <v>8760</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45805</v>
+        <v>45819</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Suspense Account 44</t>
+          <t>Suspense Account 46</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1003,75 +1003,75 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>41491.81</v>
       </c>
       <c r="H17" t="n">
-        <v>32940.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>8060</v>
+        <v>8917</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45806</v>
+        <v>45821</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Suspense Account 2</t>
+          <t>Suspense Account 42</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Adjustment per director</t>
+          <t>Prepayment release</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>70999</v>
       </c>
       <c r="H18" t="n">
-        <v>45999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>9405</v>
+        <v>9029</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45831</v>
+        <v>45824</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Suspense Account 16</t>
+          <t>Suspense Account 15</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Purchase invoice</t>
+          <t>Adjustment per director</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1083,24 +1083,24 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>33584.27</v>
+        <v>26999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>11125</v>
+        <v>9364</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45861</v>
+        <v>45830</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Suspense Account 13</t>
+          <t>Suspense Account 34</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Consultancy fee (related party)</t>
+          <t>Sales invoice</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1117,58 +1117,58 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>10999</v>
+        <v>27999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>11675</v>
+        <v>9393</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45870</v>
+        <v>45831</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Suspense Account 29</t>
+          <t>Suspense Account 16</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Write off - settlement</t>
+          <t>Purchase invoice</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>user_d</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>22999</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>11691</v>
+        <v>10027</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45872</v>
+        <v>45841</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Suspense Account 24</t>
+          <t>Suspense Account 12</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Monthly payroll</t>
+          <t>Cash advance, no invoice</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>30000</v>
+        <v>33840.53</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1190,87 +1190,87 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>12156</v>
+        <v>10892</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45880</v>
+        <v>45858</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Suspense Account 31</t>
+          <t>Suspense Account 11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Write off - settlement</t>
+          <t>Consultancy fee (related party)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>23911.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>12318</v>
+        <v>11842</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45883</v>
+        <v>45875</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Suspense Account 1</t>
+          <t>Suspense Account 32</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash advance, no invoice</t>
+          <t>Supplier payment</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>24999</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>11999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>12547</v>
+        <v>12854</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45888</v>
+        <v>45894</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Suspense Account 39</t>
+          <t>Suspense Account 19</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Monthly payroll</t>
+          <t>Cash advance, no invoice</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1280,45 +1280,45 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>74999</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>12951</v>
+        <v>13639</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45895</v>
+        <v>45906</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Suspense Account 14</t>
+          <t>Suspense Account 25</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Write off - settlement</t>
+          <t>Correction entry - reversal</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>130000</v>
+        <v>30000</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1326,67 +1326,67 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>13209</v>
+        <v>14352</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45898</v>
+        <v>45919</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Suspense Account 48</t>
+          <t>Suspense Account 40</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Cash advance, no invoice</t>
+          <t>Adjustment per director</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>77999</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>13697</v>
+        <v>15568</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45908</v>
+        <v>45942</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Suspense Account 27</t>
+          <t>Suspense Account 20</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Accrual</t>
+          <t>Purchase invoice</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>108280.8</v>
+        <v>19999</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1394,58 +1394,58 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>14020</v>
+        <v>15623</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45914</v>
+        <v>45943</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Suspense Account 3</t>
+          <t>Suspense Account 19</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Consultancy fee (related party)</t>
+          <t>Utility bill</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>manager_2</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>75999</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>62228.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>14086</v>
+        <v>15954</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45915</v>
+        <v>45949</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Suspense Account 45</t>
+          <t>Suspense Account 24</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Adjustment per director</t>
+          <t>Accrual</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1454,61 +1454,61 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="H30" t="n">
-        <v>63999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>14703</v>
+        <v>17133</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45925</v>
+        <v>45968</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Suspense Account 4</t>
+          <t>Suspense Account 8</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Prepayment release</t>
+          <t>Sales invoice</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>50000</v>
+        <v>63999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>15510</v>
+        <v>17578</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45940</v>
+        <v>45976</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Suspense Account 28</t>
+          <t>Suspense Account 48</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Adjustment per director</t>
+          <t>Consultancy fee (related party)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1522,27 +1522,27 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>23999</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>26875.75</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>16355</v>
+        <v>17676</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45955</v>
+        <v>45979</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Suspense Account 25</t>
+          <t>Suspense Account 10</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash advance, no invoice</t>
+          <t>Monthly payroll</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>130000</v>
+        <v>10999</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1564,205 +1564,239 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>16359</v>
+        <v>17799</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45955</v>
+        <v>45981</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Suspense Account 26</t>
+          <t>Suspense Account 29</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cash advance, no invoice</t>
+          <t>Customer receipt</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>user_c</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>22999</v>
       </c>
       <c r="H34" t="n">
-        <v>9141.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>16399</v>
+        <v>18362</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45957</v>
+        <v>45992</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Suspense Account 7</t>
+          <t>Suspense Account 31</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Purchase invoice</t>
+          <t>Correction entry - reversal</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_e</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H35" t="n">
-        <v>41049.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>17135</v>
+        <v>18409</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45968</v>
+        <v>45993</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Suspense Account 8</t>
+          <t>Suspense Account 28</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sales invoice</t>
+          <t>Purchase invoice</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>user_a</t>
+          <t>user_c</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>21656.16</v>
       </c>
       <c r="H36" t="n">
-        <v>130000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>17866</v>
+        <v>18650</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45982</v>
+        <v>45996</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Suspense Account 5</t>
+          <t>Suspense Account 12</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Utility bill</t>
+          <t>Consultancy fee (related party)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>71470.53999999999</v>
+        <v>69999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>18678</v>
+        <v>18687</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45996</v>
+        <v>45998</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Suspense Account 42</t>
+          <t>Suspense Account 30</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sales invoice</t>
+          <t>Cash advance, no invoice</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>user_b</t>
+          <t>user_a</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>manager_1</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>46999</v>
       </c>
       <c r="H38" t="n">
-        <v>19362.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>18686</v>
+        <v>18977</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45997</v>
+        <v>46003</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Suspense Account 3</t>
+          <t>Suspense Account 24</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Utility bill</t>
+          <t>Correction entry - reversal</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>user_d</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>user_e</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>27999</v>
+        <v>30000</v>
       </c>
       <c r="H39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>19436</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Suspense Account 21</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Purchase invoice</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>user_b</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>manager_2</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>13999</v>
+      </c>
+      <c r="H40" t="n">
         <v>0</v>
       </c>
     </row>

--- a/fixtures/idea_exports/Seldom Account Entries.xlsx
+++ b/fixtures/idea_exports/Seldom Account Entries.xlsx
@@ -1496,7 +1496,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>17578</v>
+        <v>17576</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>45976</v>
